--- a/data/MasterRecipes.xlsx
+++ b/data/MasterRecipes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sneun\Documents\GitHub\EinLexikonDerAromen-DuefteDerWelt\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48406BD6-245E-4A2C-825D-8D5CC756BFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB850328-D5D4-4272-8562-FEB647E5ED81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9705" yWindow="2820" windowWidth="21600" windowHeight="11835" xr2:uid="{BBB3FA31-A706-4764-BE0F-96E9FD4DB6A7}"/>
+    <workbookView xWindow="0" yWindow="1245" windowWidth="11670" windowHeight="11835" xr2:uid="{BBB3FA31-A706-4764-BE0F-96E9FD4DB6A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Detailausarbeitung" sheetId="2" r:id="rId1"/>
@@ -21888,9 +21888,6 @@
     <t>3 Tage</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-NUZ-001-A</t>
-  </si>
-  <si>
     <t>PlH-QR:MX-NUZ-001</t>
   </si>
   <si>
@@ -21945,9 +21942,6 @@
     <t>Glas</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-NUZ-001-B</t>
-  </si>
-  <si>
     <t>MIX-MEX-00004-G-000</t>
   </si>
   <si>
@@ -21993,9 +21987,6 @@
     <t>Nussallergie</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-NUZ-002-A</t>
-  </si>
-  <si>
     <t>PlH-QR:MX-NUZ-002</t>
   </si>
   <si>
@@ -22047,9 +22038,6 @@
     <t>Aufbewahrung max. 3 Tage</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-NUZ-002-B</t>
-  </si>
-  <si>
     <t>MIX-MEX-00006-G-000</t>
   </si>
   <si>
@@ -22089,9 +22077,6 @@
     <t>4 Tage</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-CAC-003-A</t>
-  </si>
-  <si>
     <t>PlH-QR:MX-CAC-003</t>
   </si>
   <si>
@@ -22128,9 +22113,6 @@
     <t>Kühl halten</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-CAC-003-B</t>
-  </si>
-  <si>
     <t>MIX-MEX-00005-G-000</t>
   </si>
   <si>
@@ -22167,9 +22149,6 @@
     <t>Allergie</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-ALM-004-A</t>
-  </si>
-  <si>
     <t>PlH-QR:MX-ALM-004</t>
   </si>
   <si>
@@ -22203,9 +22182,6 @@
     <t>Carne Asada, Tacos Monterrey</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-NUZ-005-A</t>
-  </si>
-  <si>
     <t>PlH-QR:MX-NUZ-005</t>
   </si>
   <si>
@@ -22239,9 +22215,6 @@
     <t>Taco Bars Monterrey</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-NUZ-005-B</t>
-  </si>
-  <si>
     <t>MIX-MEX-00002-G-000</t>
   </si>
   <si>
@@ -22299,10 +22272,37 @@
     <t>15–20 Tage</t>
   </si>
   <si>
-    <t>PlH-Illu:MX-MCH-006-A</t>
-  </si>
-  <si>
     <t>PlH-QR:MX-MCH-006</t>
+  </si>
+  <si>
+    <t>MX-NUZ-001-A</t>
+  </si>
+  <si>
+    <t>MX-NUZ-001-B</t>
+  </si>
+  <si>
+    <t>MX-NUZ-002-A</t>
+  </si>
+  <si>
+    <t>MX-NUZ-002-B</t>
+  </si>
+  <si>
+    <t>MX-CAC-003-A</t>
+  </si>
+  <si>
+    <t>MX-CAC-003-B</t>
+  </si>
+  <si>
+    <t>MX-ALM-004-A</t>
+  </si>
+  <si>
+    <t>MX-NUZ-005-A</t>
+  </si>
+  <si>
+    <t>MX-NUZ-005-B</t>
+  </si>
+  <si>
+    <t>MX-MCH-006-A</t>
   </si>
 </sst>
 </file>
@@ -39815,15 +39815,15 @@
         <v>1370</v>
       </c>
       <c r="AI224" t="s">
+        <v>4673</v>
+      </c>
+      <c r="AJ224" t="s">
         <v>4544</v>
-      </c>
-      <c r="AJ224" t="s">
-        <v>4545</v>
       </c>
     </row>
     <row r="225" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>4546</v>
+        <v>4545</v>
       </c>
       <c r="B225" t="s">
         <v>4384</v>
@@ -39832,25 +39832,25 @@
         <v>4523</v>
       </c>
       <c r="D225" t="s">
+        <v>4546</v>
+      </c>
+      <c r="E225" t="s">
         <v>4547</v>
-      </c>
-      <c r="E225" t="s">
-        <v>4548</v>
       </c>
       <c r="F225" t="s">
         <v>4341</v>
       </c>
       <c r="K225" t="s">
+        <v>4548</v>
+      </c>
+      <c r="M225" t="s">
         <v>4549</v>
       </c>
-      <c r="M225" t="s">
+      <c r="P225" t="s">
         <v>4550</v>
       </c>
-      <c r="P225" t="s">
+      <c r="Q225" t="s">
         <v>4551</v>
-      </c>
-      <c r="Q225" t="s">
-        <v>4552</v>
       </c>
       <c r="R225" t="s">
         <v>4530</v>
@@ -39868,75 +39868,75 @@
         <v>4534</v>
       </c>
       <c r="X225" t="s">
+        <v>4552</v>
+      </c>
+      <c r="Y225" t="s">
         <v>4553</v>
       </c>
-      <c r="Y225" t="s">
+      <c r="Z225" t="s">
         <v>4554</v>
       </c>
-      <c r="Z225" t="s">
+      <c r="AA225" t="s">
         <v>4555</v>
       </c>
-      <c r="AA225" t="s">
+      <c r="AB225" t="s">
         <v>4556</v>
-      </c>
-      <c r="AB225" t="s">
-        <v>4557</v>
       </c>
       <c r="AC225" t="s">
         <v>4539</v>
       </c>
       <c r="AD225" t="s">
+        <v>4557</v>
+      </c>
+      <c r="AE225" t="s">
         <v>4558</v>
       </c>
-      <c r="AE225" t="s">
+      <c r="AF225" t="s">
         <v>4559</v>
       </c>
-      <c r="AF225" t="s">
+      <c r="AG225" t="s">
         <v>4560</v>
       </c>
-      <c r="AG225" t="s">
+      <c r="AH225" t="s">
         <v>4561</v>
       </c>
-      <c r="AH225" t="s">
-        <v>4562</v>
-      </c>
       <c r="AI225" t="s">
-        <v>4563</v>
+        <v>4674</v>
       </c>
       <c r="AJ225" t="s">
-        <v>4545</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="226" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>4564</v>
+        <v>4562</v>
       </c>
       <c r="B226" t="s">
         <v>41</v>
       </c>
       <c r="C226" t="s">
+        <v>4563</v>
+      </c>
+      <c r="D226" t="s">
+        <v>4564</v>
+      </c>
+      <c r="E226" t="s">
         <v>4565</v>
-      </c>
-      <c r="D226" t="s">
-        <v>4566</v>
-      </c>
-      <c r="E226" t="s">
-        <v>4567</v>
       </c>
       <c r="F226" t="s">
         <v>4341</v>
       </c>
       <c r="K226" t="s">
+        <v>4566</v>
+      </c>
+      <c r="M226" t="s">
+        <v>4567</v>
+      </c>
+      <c r="P226" t="s">
         <v>4568</v>
       </c>
-      <c r="M226" t="s">
+      <c r="Q226" t="s">
         <v>4569</v>
-      </c>
-      <c r="P226" t="s">
-        <v>4570</v>
-      </c>
-      <c r="Q226" t="s">
-        <v>4571</v>
       </c>
       <c r="R226" t="s">
         <v>4530</v>
@@ -39954,28 +39954,28 @@
         <v>4534</v>
       </c>
       <c r="X226" t="s">
+        <v>4570</v>
+      </c>
+      <c r="Z226" t="s">
+        <v>4571</v>
+      </c>
+      <c r="AA226" t="s">
         <v>4572</v>
       </c>
-      <c r="Z226" t="s">
+      <c r="AB226" t="s">
         <v>4573</v>
-      </c>
-      <c r="AA226" t="s">
-        <v>4574</v>
-      </c>
-      <c r="AB226" t="s">
-        <v>4575</v>
       </c>
       <c r="AC226" t="s">
         <v>4539</v>
       </c>
       <c r="AD226" t="s">
+        <v>4574</v>
+      </c>
+      <c r="AE226" t="s">
+        <v>4575</v>
+      </c>
+      <c r="AF226" t="s">
         <v>4576</v>
-      </c>
-      <c r="AE226" t="s">
-        <v>4577</v>
-      </c>
-      <c r="AF226" t="s">
-        <v>4578</v>
       </c>
       <c r="AG226" t="s">
         <v>4209</v>
@@ -39984,54 +39984,54 @@
         <v>1370</v>
       </c>
       <c r="AI226" t="s">
-        <v>4579</v>
+        <v>4675</v>
       </c>
       <c r="AJ226" t="s">
-        <v>4580</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="227" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>4581</v>
+        <v>4578</v>
       </c>
       <c r="B227" t="s">
         <v>4384</v>
       </c>
       <c r="C227" t="s">
-        <v>4565</v>
+        <v>4563</v>
       </c>
       <c r="D227" t="s">
-        <v>4582</v>
+        <v>4579</v>
       </c>
       <c r="E227" t="s">
-        <v>4583</v>
+        <v>4580</v>
       </c>
       <c r="F227" t="s">
         <v>4341</v>
       </c>
       <c r="K227" t="s">
+        <v>4581</v>
+      </c>
+      <c r="M227" t="s">
+        <v>4582</v>
+      </c>
+      <c r="P227" t="s">
+        <v>4583</v>
+      </c>
+      <c r="Q227" t="s">
         <v>4584</v>
-      </c>
-      <c r="M227" t="s">
-        <v>4585</v>
-      </c>
-      <c r="P227" t="s">
-        <v>4586</v>
-      </c>
-      <c r="Q227" t="s">
-        <v>4587</v>
       </c>
       <c r="R227" t="s">
         <v>4530</v>
       </c>
       <c r="S227" t="s">
-        <v>4588</v>
+        <v>4585</v>
       </c>
       <c r="T227" t="s">
         <v>4532</v>
       </c>
       <c r="V227" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W227" t="s">
         <v>4534</v>
@@ -40040,72 +40040,72 @@
         <v>4534</v>
       </c>
       <c r="Y227" t="s">
+        <v>4587</v>
+      </c>
+      <c r="Z227" t="s">
+        <v>4588</v>
+      </c>
+      <c r="AA227" t="s">
+        <v>4589</v>
+      </c>
+      <c r="AB227" t="s">
         <v>4590</v>
-      </c>
-      <c r="Z227" t="s">
-        <v>4591</v>
-      </c>
-      <c r="AA227" t="s">
-        <v>4592</v>
-      </c>
-      <c r="AB227" t="s">
-        <v>4593</v>
       </c>
       <c r="AC227" t="s">
         <v>4539</v>
       </c>
       <c r="AD227" t="s">
-        <v>4594</v>
+        <v>4591</v>
       </c>
       <c r="AE227" t="s">
-        <v>4595</v>
+        <v>4592</v>
       </c>
       <c r="AF227" t="s">
-        <v>4596</v>
+        <v>4593</v>
       </c>
       <c r="AG227" t="s">
         <v>4543</v>
       </c>
       <c r="AH227" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="AI227" t="s">
-        <v>4597</v>
+        <v>4676</v>
       </c>
       <c r="AJ227" t="s">
-        <v>4580</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="228" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>4598</v>
+        <v>4594</v>
       </c>
       <c r="B228" t="s">
         <v>41</v>
       </c>
       <c r="C228" t="s">
-        <v>4599</v>
+        <v>4595</v>
       </c>
       <c r="D228" t="s">
-        <v>4600</v>
+        <v>4596</v>
       </c>
       <c r="E228" t="s">
-        <v>4601</v>
+        <v>4597</v>
       </c>
       <c r="F228" t="s">
         <v>4341</v>
       </c>
       <c r="K228" t="s">
-        <v>4602</v>
+        <v>4598</v>
       </c>
       <c r="M228" t="s">
-        <v>4603</v>
+        <v>4599</v>
       </c>
       <c r="P228" t="s">
-        <v>4604</v>
+        <v>4600</v>
       </c>
       <c r="Q228" t="s">
-        <v>4605</v>
+        <v>4601</v>
       </c>
       <c r="R228" t="s">
         <v>4530</v>
@@ -40117,7 +40117,7 @@
         <v>4532</v>
       </c>
       <c r="V228" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W228" t="s">
         <v>4534</v>
@@ -40126,69 +40126,69 @@
         <v>4534</v>
       </c>
       <c r="Y228" t="s">
-        <v>4606</v>
+        <v>4602</v>
       </c>
       <c r="Z228" t="s">
-        <v>4607</v>
+        <v>4603</v>
       </c>
       <c r="AA228" t="s">
-        <v>4608</v>
+        <v>4604</v>
       </c>
       <c r="AB228" t="s">
-        <v>4575</v>
+        <v>4573</v>
       </c>
       <c r="AC228" t="s">
         <v>4539</v>
       </c>
       <c r="AD228" t="s">
+        <v>4574</v>
+      </c>
+      <c r="AE228" t="s">
+        <v>4605</v>
+      </c>
+      <c r="AF228" t="s">
         <v>4576</v>
       </c>
-      <c r="AE228" t="s">
-        <v>4609</v>
-      </c>
-      <c r="AF228" t="s">
-        <v>4578</v>
-      </c>
       <c r="AG228" t="s">
-        <v>4610</v>
+        <v>4606</v>
       </c>
       <c r="AH228" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="AI228" t="s">
-        <v>4611</v>
+        <v>4677</v>
       </c>
       <c r="AJ228" t="s">
-        <v>4612</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="229" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>4613</v>
+        <v>4608</v>
       </c>
       <c r="B229" t="s">
         <v>4384</v>
       </c>
       <c r="C229" t="s">
-        <v>4599</v>
+        <v>4595</v>
       </c>
       <c r="D229" t="s">
-        <v>4614</v>
+        <v>4609</v>
       </c>
       <c r="E229" t="s">
-        <v>4615</v>
+        <v>4610</v>
       </c>
       <c r="F229" t="s">
         <v>4341</v>
       </c>
       <c r="K229" t="s">
-        <v>4616</v>
+        <v>4611</v>
       </c>
       <c r="M229" t="s">
-        <v>4569</v>
+        <v>4567</v>
       </c>
       <c r="P229" t="s">
-        <v>4617</v>
+        <v>4612</v>
       </c>
       <c r="Q229" t="s">
         <v>4344</v>
@@ -40203,7 +40203,7 @@
         <v>4532</v>
       </c>
       <c r="V229" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W229" t="s">
         <v>4534</v>
@@ -40212,69 +40212,69 @@
         <v>4534</v>
       </c>
       <c r="Y229" t="s">
-        <v>4618</v>
+        <v>4613</v>
       </c>
       <c r="Z229" t="s">
-        <v>4619</v>
+        <v>4614</v>
       </c>
       <c r="AA229" t="s">
-        <v>4620</v>
+        <v>4615</v>
       </c>
       <c r="AB229" t="s">
-        <v>4557</v>
+        <v>4556</v>
       </c>
       <c r="AC229" t="s">
         <v>4539</v>
       </c>
       <c r="AD229" t="s">
-        <v>4621</v>
+        <v>4616</v>
       </c>
       <c r="AE229" t="s">
-        <v>4622</v>
+        <v>4617</v>
       </c>
       <c r="AF229" t="s">
-        <v>4623</v>
+        <v>4618</v>
       </c>
       <c r="AG229" t="s">
         <v>3408</v>
       </c>
       <c r="AH229" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="AI229" t="s">
-        <v>4624</v>
+        <v>4678</v>
       </c>
       <c r="AJ229" t="s">
-        <v>4612</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="230" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>4625</v>
+        <v>4619</v>
       </c>
       <c r="B230" t="s">
         <v>41</v>
       </c>
       <c r="C230" t="s">
-        <v>4626</v>
+        <v>4620</v>
       </c>
       <c r="D230" t="s">
-        <v>4627</v>
+        <v>4621</v>
       </c>
       <c r="E230" t="s">
-        <v>4628</v>
+        <v>4622</v>
       </c>
       <c r="F230" t="s">
         <v>4341</v>
       </c>
       <c r="K230" t="s">
-        <v>4629</v>
+        <v>4623</v>
       </c>
       <c r="M230" t="s">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="P230" t="s">
-        <v>4630</v>
+        <v>4624</v>
       </c>
       <c r="Q230" t="s">
         <v>4344</v>
@@ -40283,13 +40283,13 @@
         <v>4530</v>
       </c>
       <c r="S230" t="s">
-        <v>4631</v>
+        <v>4625</v>
       </c>
       <c r="T230" t="s">
         <v>4532</v>
       </c>
       <c r="V230" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W230" t="s">
         <v>4534</v>
@@ -40298,84 +40298,84 @@
         <v>4534</v>
       </c>
       <c r="Y230" t="s">
-        <v>4632</v>
+        <v>4626</v>
       </c>
       <c r="Z230" t="s">
-        <v>4633</v>
+        <v>4627</v>
       </c>
       <c r="AA230" t="s">
-        <v>4634</v>
+        <v>4628</v>
       </c>
       <c r="AB230" t="s">
-        <v>4593</v>
+        <v>4590</v>
       </c>
       <c r="AC230" t="s">
         <v>4539</v>
       </c>
       <c r="AD230" t="s">
-        <v>4594</v>
+        <v>4591</v>
       </c>
       <c r="AE230" t="s">
-        <v>4635</v>
+        <v>4629</v>
       </c>
       <c r="AF230" t="s">
-        <v>4636</v>
+        <v>4630</v>
       </c>
       <c r="AG230" t="s">
         <v>4543</v>
       </c>
       <c r="AH230" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="AI230" t="s">
-        <v>4637</v>
+        <v>4679</v>
       </c>
       <c r="AJ230" t="s">
-        <v>4638</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="231" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>4639</v>
+        <v>4632</v>
       </c>
       <c r="B231" t="s">
         <v>41</v>
       </c>
       <c r="C231" t="s">
-        <v>4640</v>
+        <v>4633</v>
       </c>
       <c r="D231" t="s">
-        <v>4641</v>
+        <v>4634</v>
       </c>
       <c r="E231" t="s">
-        <v>4642</v>
+        <v>4635</v>
       </c>
       <c r="F231" t="s">
         <v>4341</v>
       </c>
       <c r="K231" t="s">
-        <v>4568</v>
+        <v>4566</v>
       </c>
       <c r="M231" t="s">
-        <v>4643</v>
+        <v>4636</v>
       </c>
       <c r="P231" t="s">
-        <v>4644</v>
+        <v>4637</v>
       </c>
       <c r="Q231" t="s">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="R231" t="s">
         <v>4530</v>
       </c>
       <c r="S231" t="s">
-        <v>4645</v>
+        <v>4638</v>
       </c>
       <c r="T231" t="s">
         <v>4532</v>
       </c>
       <c r="V231" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W231" t="s">
         <v>4534</v>
@@ -40384,72 +40384,72 @@
         <v>4534</v>
       </c>
       <c r="Y231" t="s">
-        <v>4590</v>
+        <v>4587</v>
       </c>
       <c r="Z231" t="s">
-        <v>4646</v>
+        <v>4639</v>
       </c>
       <c r="AA231" t="s">
-        <v>4647</v>
+        <v>4640</v>
       </c>
       <c r="AB231" t="s">
-        <v>4575</v>
+        <v>4573</v>
       </c>
       <c r="AC231" t="s">
         <v>4539</v>
       </c>
       <c r="AD231" t="s">
-        <v>4576</v>
+        <v>4574</v>
       </c>
       <c r="AE231" t="s">
-        <v>4648</v>
+        <v>4641</v>
       </c>
       <c r="AF231" t="s">
-        <v>4560</v>
+        <v>4559</v>
       </c>
       <c r="AG231" t="s">
         <v>4543</v>
       </c>
       <c r="AH231" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="AI231" t="s">
-        <v>4649</v>
+        <v>4680</v>
       </c>
       <c r="AJ231" t="s">
-        <v>4650</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="232" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>4651</v>
+        <v>4643</v>
       </c>
       <c r="B232" t="s">
         <v>4384</v>
       </c>
       <c r="C232" t="s">
-        <v>4640</v>
+        <v>4633</v>
       </c>
       <c r="D232" t="s">
-        <v>4652</v>
+        <v>4644</v>
       </c>
       <c r="E232" t="s">
-        <v>4653</v>
+        <v>4645</v>
       </c>
       <c r="F232" t="s">
         <v>4341</v>
       </c>
       <c r="K232" t="s">
-        <v>4654</v>
+        <v>4646</v>
       </c>
       <c r="M232" t="s">
-        <v>4655</v>
+        <v>4647</v>
       </c>
       <c r="P232" t="s">
-        <v>4656</v>
+        <v>4648</v>
       </c>
       <c r="Q232" t="s">
-        <v>4552</v>
+        <v>4551</v>
       </c>
       <c r="R232" t="s">
         <v>4530</v>
@@ -40461,7 +40461,7 @@
         <v>4532</v>
       </c>
       <c r="V232" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W232" t="s">
         <v>4534</v>
@@ -40470,84 +40470,84 @@
         <v>4534</v>
       </c>
       <c r="Y232" t="s">
-        <v>4657</v>
+        <v>4649</v>
       </c>
       <c r="Z232" t="s">
-        <v>4658</v>
+        <v>4650</v>
       </c>
       <c r="AA232" t="s">
-        <v>4659</v>
+        <v>4651</v>
       </c>
       <c r="AB232" t="s">
-        <v>4575</v>
+        <v>4573</v>
       </c>
       <c r="AC232" t="s">
         <v>4539</v>
       </c>
       <c r="AD232" t="s">
-        <v>4621</v>
+        <v>4616</v>
       </c>
       <c r="AE232" t="s">
-        <v>4660</v>
+        <v>4652</v>
       </c>
       <c r="AF232" t="s">
+        <v>4559</v>
+      </c>
+      <c r="AG232" t="s">
         <v>4560</v>
       </c>
-      <c r="AG232" t="s">
+      <c r="AH232" t="s">
         <v>4561</v>
       </c>
-      <c r="AH232" t="s">
-        <v>4562</v>
-      </c>
       <c r="AI232" t="s">
-        <v>4661</v>
+        <v>4681</v>
       </c>
       <c r="AJ232" t="s">
-        <v>4650</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="233" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>4662</v>
+        <v>4653</v>
       </c>
       <c r="B233" t="s">
         <v>41</v>
       </c>
       <c r="C233" t="s">
-        <v>4663</v>
+        <v>4654</v>
       </c>
       <c r="D233" t="s">
-        <v>4664</v>
+        <v>4655</v>
       </c>
       <c r="E233" t="s">
-        <v>4665</v>
+        <v>4656</v>
       </c>
       <c r="F233" t="s">
-        <v>4666</v>
+        <v>4657</v>
       </c>
       <c r="K233" t="s">
-        <v>4667</v>
+        <v>4658</v>
       </c>
       <c r="M233" t="s">
-        <v>4668</v>
+        <v>4659</v>
       </c>
       <c r="P233" t="s">
-        <v>4669</v>
+        <v>4660</v>
       </c>
       <c r="Q233" t="s">
-        <v>4670</v>
+        <v>4661</v>
       </c>
       <c r="R233" t="s">
         <v>4530</v>
       </c>
       <c r="S233" t="s">
-        <v>4671</v>
+        <v>4662</v>
       </c>
       <c r="T233" t="s">
         <v>4532</v>
       </c>
       <c r="V233" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
       <c r="W233" t="s">
         <v>4534</v>
@@ -40556,40 +40556,40 @@
         <v>4534</v>
       </c>
       <c r="Y233" t="s">
+        <v>4663</v>
+      </c>
+      <c r="Z233" t="s">
+        <v>4664</v>
+      </c>
+      <c r="AA233" t="s">
+        <v>4665</v>
+      </c>
+      <c r="AB233" t="s">
+        <v>4666</v>
+      </c>
+      <c r="AC233" t="s">
+        <v>4667</v>
+      </c>
+      <c r="AD233" t="s">
+        <v>4668</v>
+      </c>
+      <c r="AE233" t="s">
+        <v>4669</v>
+      </c>
+      <c r="AF233" t="s">
+        <v>4670</v>
+      </c>
+      <c r="AG233" t="s">
+        <v>4671</v>
+      </c>
+      <c r="AH233" t="s">
+        <v>4561</v>
+      </c>
+      <c r="AI233" t="s">
+        <v>4682</v>
+      </c>
+      <c r="AJ233" t="s">
         <v>4672</v>
-      </c>
-      <c r="Z233" t="s">
-        <v>4673</v>
-      </c>
-      <c r="AA233" t="s">
-        <v>4674</v>
-      </c>
-      <c r="AB233" t="s">
-        <v>4675</v>
-      </c>
-      <c r="AC233" t="s">
-        <v>4676</v>
-      </c>
-      <c r="AD233" t="s">
-        <v>4677</v>
-      </c>
-      <c r="AE233" t="s">
-        <v>4678</v>
-      </c>
-      <c r="AF233" t="s">
-        <v>4679</v>
-      </c>
-      <c r="AG233" t="s">
-        <v>4680</v>
-      </c>
-      <c r="AH233" t="s">
-        <v>4562</v>
-      </c>
-      <c r="AI233" t="s">
-        <v>4681</v>
-      </c>
-      <c r="AJ233" t="s">
-        <v>4682</v>
       </c>
     </row>
   </sheetData>
